--- a/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -128,10 +128,13 @@
     <t>ClinicalDocument</t>
   </si>
   <si>
-    <t>FRLMHeaderDocument.identifier</t>
+    <t>FRLMHeaderDocument.identifier:document</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.identifier:versionSet</t>
   </si>
   <si>
     <t>ClinicalDocument.setId</t>
@@ -647,274 +650,274 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2"/>
     </row>
@@ -956,7 +959,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -971,7 +974,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1013,7 +1016,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1021,274 +1024,274 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E23" s="2"/>
     </row>

--- a/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,13 +110,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-header-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-header-document|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-clinical-document</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-clinical-document|0.1.0</t>
   </si>
   <si>
     <t>FRLMHeaderDocument</t>
@@ -260,13 +260,13 @@
     <t>ClinicalDocument.componentOf</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-bundle-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-bundle-document|0.1.0</t>
   </si>
   <si>
     <t>Bundle.identifier</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>Composition.type</t>

--- a/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,7 +110,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-header-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHeaderDocument|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -128,15 +128,12 @@
     <t>ClinicalDocument</t>
   </si>
   <si>
-    <t>FRLMHeaderDocument.identifier:document</t>
+    <t>FRLMHeaderDocument.identifier</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
   </si>
   <si>
-    <t>FRLMHeaderDocument.identifier:versionSet</t>
-  </si>
-  <si>
     <t>ClinicalDocument.setId</t>
   </si>
   <si>
@@ -194,7 +191,7 @@
     <t>ClinicalDocument.recordTarget</t>
   </si>
   <si>
-    <t>FRLMHeaderDocument.author</t>
+    <t>FRLMHeaderDocument.author[x]</t>
   </si>
   <si>
     <t>ClinicalDocument.author</t>
@@ -650,274 +647,274 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
     </row>
@@ -959,7 +956,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -974,7 +971,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1016,7 +1013,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1024,274 +1021,274 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E23" s="2"/>
     </row>

--- a/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/main/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="117">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,6 +257,24 @@
     <t>ClinicalDocument.componentOf</t>
   </si>
   <si>
+    <t>FRLMHeaderDocument.documentReference</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.relatedDocument</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.documentReference.relationType</t>
+  </si>
+  <si>
+    <t>RelatedDocument.typeCode</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.documentReference.targetDocument[x]</t>
+  </si>
+  <si>
+    <t>RelatedDocument.parentDocument</t>
+  </si>
+  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-bundle-document|0.1.0</t>
   </si>
   <si>
@@ -327,6 +345,30 @@
   </si>
   <si>
     <t>Composition.encounter</t>
+  </si>
+  <si>
+    <t>FRLMHeaderDocument.presentedForm</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>Composition.section</t>
+  </si>
+  <si>
+    <t>FRCompositionDocument.section:sectionPresentedForm</t>
+  </si>
+  <si>
+    <t>Composition.extension:diagnosticReport.presentedForm</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo.code</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo.target[x]</t>
   </si>
 </sst>
 </file>
@@ -582,7 +624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -917,6 +959,45 @@
         <v>78</v>
       </c>
       <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E28" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -956,7 +1037,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -971,7 +1052,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -982,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1094,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1028,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1041,7 +1122,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1054,7 +1135,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1067,7 +1148,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1080,7 +1161,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1093,7 +1174,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -1106,7 +1187,7 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -1119,7 +1200,7 @@
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1132,7 +1213,7 @@
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -1145,7 +1226,7 @@
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1158,7 +1239,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -1171,7 +1252,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1184,7 +1265,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -1197,7 +1278,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1210,7 +1291,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1223,7 +1304,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1236,7 +1317,7 @@
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -1249,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2"/>
     </row>
@@ -1262,7 +1343,7 @@
         <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2"/>
     </row>
@@ -1275,7 +1356,7 @@
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E22" s="2"/>
     </row>
@@ -1288,9 +1369,76 @@
         <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E28" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
